--- a/docs/fluorsight-model.xlsx
+++ b/docs/fluorsight-model.xlsx
@@ -19,10 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -34,7 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B0B0B"/>
       <sz val="15"/>
     </font>
     <font>
@@ -45,7 +43,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,8 +54,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="000B0B0B"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -69,17 +74,9 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -126,12 +123,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,21 +137,17 @@
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -259,7 +252,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Model'!B27</f>
+              <f>'Model'!B29</f>
             </strRef>
           </tx>
           <spPr>
@@ -273,12 +266,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Model'!$A$28:$A$29</f>
+              <f>'Model'!$A$30:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Model'!$B$28:$B$29</f>
+              <f>'Model'!$B$30:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -287,7 +280,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Model'!C27</f>
+              <f>'Model'!C29</f>
             </strRef>
           </tx>
           <spPr>
@@ -301,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Model'!$A$28:$A$29</f>
+              <f>'Model'!$A$30:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Model'!$C$28:$C$29</f>
+              <f>'Model'!$C$30:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -315,7 +308,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Model'!D27</f>
+              <f>'Model'!D29</f>
             </strRef>
           </tx>
           <spPr>
@@ -329,12 +322,40 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Model'!$A$28:$A$29</f>
+              <f>'Model'!$A$30:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Model'!$D$28:$D$29</f>
+              <f>'Model'!$D$30:$D$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Model'!E29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Model'!$A$30:$A$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Model'!$E$30:$E$31</f>
             </numRef>
           </val>
         </ser>
@@ -405,7 +426,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>The saving holds across the escalation rate we are least sure of</a:t>
+              <a:t>The saving holds across the rate we are least sure of</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -649,7 +670,168 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>What we charge: their saving against our revenue</a:t>
+              <a:t>Small customers: the subscription, not the device, is what hurts</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Sensitivity'!M5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sensitivity'!$L$6:$L$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sensitivity'!$M$6:$M$13</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Sensitivity'!N5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sensitivity'!$L$6:$L$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sensitivity'!$N$6:$N$13</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Customer's annual sample volume</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Customer saving</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>What we charge per refill: their saving against our revenue</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -883,6 +1065,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1187,7 +1391,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Charts — copy any of these straight into PowerPoint</t>
         </is>
@@ -1196,7 +1400,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Right-click a chart → Copy, then paste into a slide. They stay linked to this workbook, so changing an assumption updates the slide. Data lives on the Model and Sensitivity sheets.</t>
+          <t>Right-click → Copy, paste into a slide. They stay linked to this workbook, so changing an assumption updates the slide. Data is on the Model and Sensitivity sheets.</t>
         </is>
       </c>
     </row>
@@ -1212,14 +1416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1232,7 +1436,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Change any yellow cell. Every figure and chart in this workbook updates. Nothing here is hard-coded downstream.</t>
+          <t>Change any yellow cell. Everything else in this workbook is a formula and will follow.</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1488,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Illustrative annual programme for one consultancy. Our choice, not measured.</t>
+          <t>Illustrative annual programme for one customer. Our choice.</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1513,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>The weakest assumption in the model. Shown as a range on the Sensitivity sheet.</t>
+          <t>The weakest assumption in the model. See Sensitivity table A.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1538,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>No UK laboratory publishes a rate card — 7 providers' published pricing checked, all quote on request.</t>
+          <t>No UK lab publishes a rate card — 7 providers' published pricing checked, all quote on request.</t>
         </is>
       </c>
     </row>
@@ -1359,14 +1563,14 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Our pricing decision. Standard single-programme tier.</t>
+          <t>Pricing decision. Set to 0 to model pure device-and-refills — see Sensitivity table D.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consumable price to customer</t>
+          <t>Refill price to customer</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -1384,14 +1588,14 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>What we charge per screen. A pricing decision, not a cost.</t>
+          <t>What we charge per screen. A price, not a cost.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consumable cost to us</t>
+          <t>Refill cost to us</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1424,7 +1628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£ one-off</t>
+          <t>£ / device</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1438,82 +1642,126 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Device price to customer</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£ / device</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — no pricing decision has been made. Change this.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Reference — not an input</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PUBLISHED</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lab turnaround</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>10–15 working days</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PUBLISHED</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>SOCOTEC UK, PFAS testing page, checked Sept 2026.</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Devices per customer</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>devices</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — one reader per customer. A field team may need several.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Published water price (Finland)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>€175–300 / sample</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PUBLISHED</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Measurlabs list price. Not UK, and not a like-for-like scope.</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Reference — context, not inputs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Lab turnaround</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10–15 working days</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>SOCOTEC UK PFAS page, checked Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Published water price (Finland)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>€175–300 / sample</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Measurlabs list price. Not UK, not like-for-like scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Nearest published UK figure</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>£350 / sample</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>EIA evidence to Commons EAC, May 2025 — for SOIL, explicitly excludes water. Does NOT validate the £250 above.</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>EIA to Commons EAC, May 2025 — SOIL, explicitly excludes water. Does NOT validate the £250.</t>
         </is>
       </c>
     </row>
@@ -1528,25 +1776,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The model — one 500-sample programme</t>
+          <t>The model — one customer, one year</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every cell is a formula. Change the Assumptions sheet and these move.</t>
+          <t>Every cell is a formula off the Assumptions sheet.</t>
         </is>
       </c>
     </row>
@@ -1556,8 +1804,8 @@
           <t>What the customer pays</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1565,13 +1813,13 @@
           <t>Testing everything at the lab</t>
         </is>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <f>Assumptions!B6*Assumptions!B8</f>
         <v/>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Portfolio × lab cost. The do-nothing baseline.</t>
+          <t>The do-nothing baseline: portfolio × lab cost.</t>
         </is>
       </c>
     </row>
@@ -1581,14 +1829,9 @@
           <t>Samples escalated to the lab</t>
         </is>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <f>ROUND(Assumptions!B6*Assumptions!B7,0)</f>
         <v/>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Portfolio × escalation rate.</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -1597,25 +1840,24 @@
           <t xml:space="preserve">  Lab spend under triage</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <f>B7*Assumptions!B8</f>
         <v/>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Screening consumables</t>
-        </is>
-      </c>
-      <c r="B9" s="9">
+          <t xml:space="preserve">  Screening refills</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
         <f>Assumptions!B6*Assumptions!B10</f>
         <v/>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Every sample is screened, so this is the full portfolio.</t>
+          <t>Every sample is screened, so this is the whole portfolio.</t>
         </is>
       </c>
     </row>
@@ -1625,211 +1867,245 @@
           <t xml:space="preserve">  Software subscription</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <f>Assumptions!B9</f>
         <v/>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Devices</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <f>Assumptions!B13*Assumptions!B14</f>
+        <v/>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>One-off. A durable reader, not a per-year cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Total with Fluorsight</t>
         </is>
       </c>
-      <c r="B11" s="12">
-        <f>B8+B9+B10</f>
-        <v/>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="B12" s="13">
+        <f>B8+B9+B10+B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Customer saving</t>
         </is>
       </c>
-      <c r="B12" s="14">
-        <f>B6-B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="B13" s="15">
+        <f>B6-B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Saving as a share</t>
         </is>
       </c>
-      <c r="B13" s="15">
-        <f>B12/B6</f>
-        <v/>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B14" s="16">
+        <f>B13/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>What it means for us</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
-        <f>Assumptions!B9+Assumptions!B6*Assumptions!B10</f>
-        <v/>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Subscription plus what we charge per screen.</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cost of goods</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>Assumptions!B6*Assumptions!B11</f>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>Assumptions!B9+Assumptions!B6*Assumptions!B10+Assumptions!B13*Assumptions!B14</f>
         <v/>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Portfolio × our per-sample cost.</t>
+          <t>Subscription + refills + device sale.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Cost of goods</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>Assumptions!B6*Assumptions!B11+Assumptions!B14*Assumptions!B12</f>
+        <v/>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Refills + devices, at our cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B18" s="9">
-        <f>B16-B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>B18/B16</f>
-        <v/>
-      </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="B19" s="13">
+        <f>B17-B18</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Device payback</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B20" s="17">
-        <f>Assumptions!B12/(Assumptions!B10-Assumptions!B11)</f>
-        <v/>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Screens needed to cover the one-off £40 device.</t>
-        </is>
+        <f>B19/B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  margin on the device alone</t>
+        </is>
+      </c>
+      <c r="B21" s="10">
+        <f>Assumptions!B14*(Assumptions!B13-Assumptions!B12)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  device as a share of revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="17">
+        <f>Assumptions!B13*Assumptions!B14/B17</f>
+        <v/>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>If this reads ~1%, the razor-and-blades story is about the refills, not the razor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>The robustness test</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Break-even lab cost</t>
         </is>
       </c>
-      <c r="B23" s="9">
-        <f>(Assumptions!B9+Assumptions!B6*Assumptions!B10)/(Assumptions!B6*(1-Assumptions!B7))</f>
-        <v/>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Triage stops paying only if lab analysis falls below this. We assume £250 — so the conclusion survives being badly wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="B25" s="10">
+        <f>(Assumptions!B6*Assumptions!B10+Assumptions!B9+Assumptions!B13*Assumptions!B14)/(Assumptions!B6*(1-Assumptions!B7))</f>
+        <v/>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Triage stops paying only if lab analysis falls below this. We assume £250, so the conclusion survives being badly wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Chart data — cost comparison</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Lab analysis</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Refills</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Subscription</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Test everything</t>
         </is>
       </c>
-      <c r="B28" s="9">
+      <c r="B30" s="10">
         <f>B6</f>
         <v/>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C30" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D30" s="10" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>With Fluorsight</t>
         </is>
       </c>
-      <c r="B29" s="9">
+      <c r="B31" s="10">
         <f>B8</f>
         <v/>
       </c>
-      <c r="C29" s="9">
+      <c r="C31" s="10">
         <f>B9</f>
         <v/>
       </c>
-      <c r="D29" s="9">
+      <c r="D31" s="10">
         <f>B10</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>B11</f>
         <v/>
       </c>
     </row>
@@ -1844,23 +2120,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sensitivity — what happens when the assumptions are wrong</t>
         </is>
@@ -1869,452 +2149,567 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Three tables, all live off the Assumptions sheet. These feed the charts.</t>
+          <t>All live off the Assumptions sheet. These four tables feed the charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="L3" s="19" t="inlineStr">
+        <is>
+          <t>The subscription is fixed, so it swamps a small programme. Set the subscription to 0 and watch the blue line flatten onto the orange one.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>A · If more samples escalate than we assume</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>B · Break-even — how cheap would the lab have to get?</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>C · What we charge — their saving against our revenue</t>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>C · What we charge per refill</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>D · Does the saving hold for a SMALL customer?</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Escalation rate</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Customer saving (£)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Saving (%)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Lab cost (£/sample)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Net saving (£)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>Price per screen (£)</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Refill price (£)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Customer saving (£)</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Our revenue (£)</t>
         </is>
       </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Samples / year</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Saving with subscription</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Saving, refills only</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="20" t="n">
         <v>0.05</v>
       </c>
-      <c r="B6" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A6,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C6" s="16">
+      <c r="B6" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A6,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C6" s="17">
         <f>B6/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="9">
-        <f>Assumptions!$B$6*E6-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E6+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H6" s="9" t="n">
+      <c r="F6" s="10">
+        <f>Assumptions!$B$6*E6-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E6+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H6+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J6" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H6</f>
+      <c r="I6" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H6+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J6" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H6+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v>25</v>
+      </c>
+      <c r="M6" s="17">
+        <f>(L6*Assumptions!$B$8-(ROUND(L6*Assumptions!$B$7,0)*Assumptions!$B$8+L6*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L6*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N6" s="17">
+        <f>(L6*Assumptions!$B$8-(ROUND(L6*Assumptions!$B$7,0)*Assumptions!$B$8+L6*Assumptions!$B$10+Model!$B$11))/(L6*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="B7" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A7,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C7" s="16">
+      <c r="B7" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A7,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C7" s="17">
         <f>B7/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="9">
-        <f>Assumptions!$B$6*E7-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E7+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H7" s="9" t="n">
+      <c r="F7" s="10">
+        <f>Assumptions!$B$6*E7-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E7+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H7+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J7" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H7</f>
+      <c r="I7" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H7+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J7" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H7+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" s="17">
+        <f>(L7*Assumptions!$B$8-(ROUND(L7*Assumptions!$B$7,0)*Assumptions!$B$8+L7*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L7*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N7" s="17">
+        <f>(L7*Assumptions!$B$8-(ROUND(L7*Assumptions!$B$7,0)*Assumptions!$B$8+L7*Assumptions!$B$10+Model!$B$11))/(L7*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="B8" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A8,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C8" s="16">
+      <c r="B8" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A8,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
         <f>B8/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="F8" s="9">
-        <f>Assumptions!$B$6*E8-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H8" s="9" t="n">
+      <c r="F8" s="10">
+        <f>Assumptions!$B$6*E8-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H8+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J8" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H8</f>
+      <c r="I8" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H8+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J8" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H8+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v>100</v>
+      </c>
+      <c r="M8" s="17">
+        <f>(L8*Assumptions!$B$8-(ROUND(L8*Assumptions!$B$7,0)*Assumptions!$B$8+L8*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L8*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="17">
+        <f>(L8*Assumptions!$B$8-(ROUND(L8*Assumptions!$B$7,0)*Assumptions!$B$8+L8*Assumptions!$B$10+Model!$B$11))/(L8*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="B9" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A9,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="16">
+      <c r="B9" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A9,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
         <f>B9/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="F9" s="9">
-        <f>Assumptions!$B$6*E9-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E9+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="9" t="n">
+      <c r="F9" s="10">
+        <f>Assumptions!$B$6*E9-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E9+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H9" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H9+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H9</f>
+      <c r="I9" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J9" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H9+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v>200</v>
+      </c>
+      <c r="M9" s="17">
+        <f>(L9*Assumptions!$B$8-(ROUND(L9*Assumptions!$B$7,0)*Assumptions!$B$8+L9*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L9*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N9" s="17">
+        <f>(L9*Assumptions!$B$8-(ROUND(L9*Assumptions!$B$7,0)*Assumptions!$B$8+L9*Assumptions!$B$10+Model!$B$11))/(L9*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="B10" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A10,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="16">
+      <c r="B10" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A10,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
         <f>B10/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="F10" s="9">
-        <f>Assumptions!$B$6*E10-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E10+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="9" t="n">
+      <c r="F10" s="10">
+        <f>Assumptions!$B$6*E10-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E10+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H10" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="I10" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J10" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H10</f>
+      <c r="I10" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H10+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J10" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H10+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v>300</v>
+      </c>
+      <c r="M10" s="17">
+        <f>(L10*Assumptions!$B$8-(ROUND(L10*Assumptions!$B$7,0)*Assumptions!$B$8+L10*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L10*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N10" s="17">
+        <f>(L10*Assumptions!$B$8-(ROUND(L10*Assumptions!$B$7,0)*Assumptions!$B$8+L10*Assumptions!$B$10+Model!$B$11))/(L10*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="B11" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A11,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C11" s="16">
+      <c r="B11" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A11,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
         <f>B11/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="F11" s="9">
-        <f>Assumptions!$B$6*E11-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E11+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H11" s="9" t="n">
+      <c r="F11" s="10">
+        <f>Assumptions!$B$6*E11-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E11+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="I11" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H11+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J11" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H11</f>
+      <c r="I11" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H11+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H11+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L11" t="n">
+        <v>500</v>
+      </c>
+      <c r="M11" s="17">
+        <f>(L11*Assumptions!$B$8-(ROUND(L11*Assumptions!$B$7,0)*Assumptions!$B$8+L11*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L11*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N11" s="17">
+        <f>(L11*Assumptions!$B$8-(ROUND(L11*Assumptions!$B$7,0)*Assumptions!$B$8+L11*Assumptions!$B$10+Model!$B$11))/(L11*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="20" t="n">
         <v>0.35</v>
       </c>
-      <c r="B12" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A12,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C12" s="16">
+      <c r="B12" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A12,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
         <f>B12/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="F12" s="9">
-        <f>Assumptions!$B$6*E12-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E12+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H12" s="9" t="n">
+      <c r="F12" s="10">
+        <f>Assumptions!$B$6*E12-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E12+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="I12" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H12+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J12" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H12</f>
+      <c r="I12" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H12+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H12+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>750</v>
+      </c>
+      <c r="M12" s="17">
+        <f>(L12*Assumptions!$B$8-(ROUND(L12*Assumptions!$B$7,0)*Assumptions!$B$8+L12*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L12*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N12" s="17">
+        <f>(L12*Assumptions!$B$8-(ROUND(L12*Assumptions!$B$7,0)*Assumptions!$B$8+L12*Assumptions!$B$10+Model!$B$11))/(L12*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="20" t="n">
         <v>0.4</v>
       </c>
-      <c r="B13" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A13,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C13" s="16">
+      <c r="B13" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A13,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
         <f>B13/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="F13" s="9">
-        <f>Assumptions!$B$6*E13-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E13+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H13" s="9" t="n">
+      <c r="F13" s="10">
+        <f>Assumptions!$B$6*E13-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E13+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="I13" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H13+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J13" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H13</f>
+      <c r="I13" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H13+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J13" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H13+Model!$B$11</f>
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="17">
+        <f>(L13*Assumptions!$B$8-(ROUND(L13*Assumptions!$B$7,0)*Assumptions!$B$8+L13*Assumptions!$B$10+Assumptions!$B$9+Model!$B$11))/(L13*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N13" s="17">
+        <f>(L13*Assumptions!$B$8-(ROUND(L13*Assumptions!$B$7,0)*Assumptions!$B$8+L13*Assumptions!$B$10+Model!$B$11))/(L13*Assumptions!$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="20" t="n">
         <v>0.45</v>
       </c>
-      <c r="B14" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A14,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C14" s="16">
+      <c r="B14" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A14,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
         <f>B14/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>225</v>
       </c>
-      <c r="F14" s="9">
-        <f>Assumptions!$B$6*E14-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E14+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H14" s="9" t="n">
+      <c r="F14" s="10">
+        <f>Assumptions!$B$6*E14-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E14+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H14" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="I14" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H14+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J14" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H14</f>
+      <c r="I14" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H14+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J14" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H14+Model!$B$11</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="B15" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A15,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C15" s="16">
+      <c r="B15" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A15,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
         <f>B15/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="F15" s="9">
-        <f>Assumptions!$B$6*E15-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E15+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H15" s="9" t="n">
+      <c r="F15" s="10">
+        <f>Assumptions!$B$6*E15-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E15+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H15" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="I15" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H15+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J15" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H15</f>
+      <c r="I15" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H15+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J15" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H15+Model!$B$11</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="20" t="n">
         <v>0.55</v>
       </c>
-      <c r="B16" s="9">
-        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A16,0)*Assumptions!$B$8+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="C16" s="16">
+      <c r="B16" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A16,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
         <f>B16/Model!$B$6</f>
         <v/>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>275</v>
       </c>
-      <c r="F16" s="9">
-        <f>Assumptions!$B$6*E16-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E16+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="H16" s="9" t="n">
+      <c r="F16" s="10">
+        <f>Assumptions!$B$6*E16-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E16+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="H16" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="I16" s="9">
-        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H16+Assumptions!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J16" s="9">
-        <f>Assumptions!$B$9+Assumptions!$B$6*H16</f>
+      <c r="I16" s="10">
+        <f>Model!$B$6-(Model!$B$8+Assumptions!$B$6*H16+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="J16" s="10">
+        <f>Assumptions!$B$9+Assumptions!$B$6*H16+Model!$B$11</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="F17" s="9">
-        <f>Assumptions!$B$6*E17-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E17+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
+      <c r="F17" s="10">
+        <f>Assumptions!$B$6*E17-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E17+Model!$B$9+Model!$B$10+Model!$B$11)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <v>325</v>
       </c>
-      <c r="F18" s="9">
-        <f>Assumptions!$B$6*E18-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E18+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
+      <c r="F18" s="10">
+        <f>Assumptions!$B$6*E18-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E18+Model!$B$9+Model!$B$10+Model!$B$11)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="F19" s="9">
-        <f>Assumptions!$B$6*E19-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E19+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
+      <c r="F19" s="10">
+        <f>Assumptions!$B$6*E19-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E19+Model!$B$9+Model!$B$10+Model!$B$11)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>375</v>
       </c>
-      <c r="F20" s="9">
-        <f>Assumptions!$B$6*E20-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E20+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
+      <c r="F20" s="10">
+        <f>Assumptions!$B$6*E20-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E20+Model!$B$9+Model!$B$10+Model!$B$11)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="F21" s="9">
-        <f>Assumptions!$B$6*E21-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E21+Assumptions!$B$6*Assumptions!$B$10+Assumptions!$B$9)</f>
+      <c r="F21" s="10">
+        <f>Assumptions!$B$6*E21-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E21+Model!$B$9+Model!$B$10+Model!$B$11)</f>
         <v/>
       </c>
     </row>

--- a/docs/fluorsight-model.xlsx
+++ b/docs/fluorsight-model.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pricing options" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,6 +150,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -234,7 +238,12 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t>One 500-sample programme: £125,000 becomes £50,000</a:t>
@@ -331,34 +340,32 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Model'!E29</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EDA100"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Model'!$A$30:$A$31</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Model'!$E$30:$E$31</f>
-            </numRef>
-          </val>
-        </ser>
+        <dLbls>
+          <numFmt formatCode="&quot;£&quot;#,##0"/>
+          <txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t/>
+              </a:r>
+              <a:endParaRPr sz="1000"/>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
         <gapWidth val="60"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -371,8 +378,34 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <numFmt formatCode="General" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -383,14 +416,28 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Annual cost</a:t>
@@ -398,19 +445,75 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
-        <numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
+        <numFmt formatCode="&quot;£&quot;#,##0,&quot;k&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="950" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="950"/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -423,7 +526,12 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t>The saving holds across the rate we are least sure of</a:t>
@@ -484,10 +592,15 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Share of screened samples sent to the lab</a:t>
@@ -495,9 +608,36 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -508,14 +648,28 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Customer saving</a:t>
@@ -523,16 +677,54 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -545,7 +737,12 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t>Triage stops paying only below ~£62.50 a sample. We assume £250.</a:t>
@@ -606,10 +803,15 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>What the laboratory charges per sample</a:t>
@@ -617,9 +819,36 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
+        <numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -630,14 +859,28 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Net saving</a:t>
@@ -645,16 +888,54 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
-        <numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
+        <numFmt formatCode="&quot;£&quot;#,##0,&quot;k&quot;" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -667,7 +948,12 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t>Small customers: the subscription, not the device, is what hurts</a:t>
@@ -764,10 +1050,15 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Customer's annual sample volume</a:t>
@@ -775,9 +1066,36 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -788,14 +1106,28 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Customer saving</a:t>
@@ -803,19 +1135,75 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="950" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="950"/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -828,7 +1216,12 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t>What we charge per refill: their saving against our revenue</a:t>
@@ -925,10 +1318,15 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Price we charge per screen</a:t>
@@ -936,9 +1334,36 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
+        <numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -949,34 +1374,820 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>Annual £</a:t>
+                  <a:t>Annual revenue</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="&quot;£&quot;#,##0,&quot;k&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="950" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="950"/>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Customer saving by size — a fixed fee is what breaks the small end</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!B36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$37:$A$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$B$37:$B$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!C36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$37:$A$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$C$37:$C$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!D36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$37:$A$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$D$37:$D$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!E36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$37:$A$45</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$E$37:$E$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>Customer's annual sample volume</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>Customer saving</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="950" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="950"/>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1250" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Effective cost per screen against the price of one lab test</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!B49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$50:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$B$50:$B$58</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!C49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$50:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$C$50:$C$58</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!D49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$50:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$D$50:$D$58</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!E49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$50:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$E$50:$E$58</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Pricing options'!F49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="94A3B8"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Pricing options'!$A$50:$A$58</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Pricing options'!$F$50:$F$58</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>Customer's annual sample volume</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="E4E4E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr rot="-5400000" vert="horz" anchor="ctr" anchorCtr="1"/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="52514E"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>Cost per screen</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
         </title>
         <numFmt formatCode="&quot;£&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="C9C9C4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="950" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="950"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="950" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="950"/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -989,7 +2200,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="5940000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1011,7 +2222,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="5940000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1033,7 +2244,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="5940000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1055,7 +2266,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="5940000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1077,7 +2288,7 @@
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="5940000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1087,6 +2298,55 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5940000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5940000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1384,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1401,6 +2661,13 @@
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Right-click → Copy, paste into a slide. They stay linked to this workbook, so changing an assumption updates the slide. Data is on the Model and Sensitivity sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Two more charts live on the 'Pricing options' sheet, next to the tier table they respond to.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2060,11 +3327,6 @@
           <t>Subscription</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2076,15 +3338,8 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2102,10 +3357,6 @@
       </c>
       <c r="D31" s="10">
         <f>B10</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>B11</f>
         <v/>
       </c>
     </row>
@@ -2716,4 +3967,947 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing structures — what each one does to a small customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A fixed annual fee spread over few screens is what breaks the small end. Edit the yellow cells and watch the tables and both charts move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>A · Today</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fixed annual fee</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Price per screen</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>B · Flat per-screen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Price per screen</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>C · Small base + per-screen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Base annual fee</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Price per screen</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>D · Tiers — a tier's price applies from its included volume; anything above is charged as overage</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Screens included</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Annual price</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pay as you go</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Programme</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>500</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Overage, per screen above the tier</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>1 · What the customer pays us (including the device)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Samples / year</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>A · Today</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>B · Flat per-screen</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>C · Base + per-screen</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>D · Tiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B24" s="10">
+        <f>$C$5+$C$6*$A24+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C24" s="10">
+        <f>$C$7*$A24+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D24" s="10">
+        <f>$C$8+$C$9*$A24+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E24" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A24,$B$13:$B$18,1))+MAX(0,$A24-INDEX($B$13:$B$18,MATCH($A24,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B25" s="10">
+        <f>$C$5+$C$6*$A25+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C25" s="10">
+        <f>$C$7*$A25+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D25" s="10">
+        <f>$C$8+$C$9*$A25+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E25" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A25,$B$13:$B$18,1))+MAX(0,$A25-INDEX($B$13:$B$18,MATCH($A25,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>100</v>
+      </c>
+      <c r="B26" s="10">
+        <f>$C$5+$C$6*$A26+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C26" s="10">
+        <f>$C$7*$A26+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f>$C$8+$C$9*$A26+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A26,$B$13:$B$18,1))+MAX(0,$A26-INDEX($B$13:$B$18,MATCH($A26,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>150</v>
+      </c>
+      <c r="B27" s="10">
+        <f>$C$5+$C$6*$A27+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C27" s="10">
+        <f>$C$7*$A27+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D27" s="10">
+        <f>$C$8+$C$9*$A27+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E27" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A27,$B$13:$B$18,1))+MAX(0,$A27-INDEX($B$13:$B$18,MATCH($A27,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>200</v>
+      </c>
+      <c r="B28" s="10">
+        <f>$C$5+$C$6*$A28+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C28" s="10">
+        <f>$C$7*$A28+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D28" s="10">
+        <f>$C$8+$C$9*$A28+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E28" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A28,$B$13:$B$18,1))+MAX(0,$A28-INDEX($B$13:$B$18,MATCH($A28,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>300</v>
+      </c>
+      <c r="B29" s="10">
+        <f>$C$5+$C$6*$A29+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C29" s="10">
+        <f>$C$7*$A29+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D29" s="10">
+        <f>$C$8+$C$9*$A29+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E29" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A29,$B$13:$B$18,1))+MAX(0,$A29-INDEX($B$13:$B$18,MATCH($A29,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>500</v>
+      </c>
+      <c r="B30" s="10">
+        <f>$C$5+$C$6*$A30+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C30" s="10">
+        <f>$C$7*$A30+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D30" s="10">
+        <f>$C$8+$C$9*$A30+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E30" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A30,$B$13:$B$18,1))+MAX(0,$A30-INDEX($B$13:$B$18,MATCH($A30,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>750</v>
+      </c>
+      <c r="B31" s="10">
+        <f>$C$5+$C$6*$A31+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C31" s="10">
+        <f>$C$7*$A31+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D31" s="10">
+        <f>$C$8+$C$9*$A31+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A31,$B$13:$B$18,1))+MAX(0,$A31-INDEX($B$13:$B$18,MATCH($A31,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B32" s="10">
+        <f>$C$5+$C$6*$A32+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="C32" s="10">
+        <f>$C$7*$A32+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="D32" s="10">
+        <f>$C$8+$C$9*$A32+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+      <c r="E32" s="10">
+        <f>INDEX($C$13:$C$18,MATCH($A32,$B$13:$B$18,1))+MAX(0,$A32-INDEX($B$13:$B$18,MATCH($A32,$B$13:$B$18,1)))*$C$19+Assumptions!$B$13*Assumptions!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2 · Customer saving against testing everything at the lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Samples / year</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>A · Today</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>B · Flat per-screen</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>C · Base + per-screen</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>D · Tiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="17">
+        <f>($A37*Assumptions!$B$8-(ROUND($A37*Assumptions!$B$7,0)*Assumptions!$B$8+B24))/($A37*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>($A37*Assumptions!$B$8-(ROUND($A37*Assumptions!$B$7,0)*Assumptions!$B$8+C24))/($A37*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>($A37*Assumptions!$B$8-(ROUND($A37*Assumptions!$B$7,0)*Assumptions!$B$8+D24))/($A37*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>($A37*Assumptions!$B$8-(ROUND($A37*Assumptions!$B$7,0)*Assumptions!$B$8+E24))/($A37*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>50</v>
+      </c>
+      <c r="B38" s="17">
+        <f>($A38*Assumptions!$B$8-(ROUND($A38*Assumptions!$B$7,0)*Assumptions!$B$8+B25))/($A38*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>($A38*Assumptions!$B$8-(ROUND($A38*Assumptions!$B$7,0)*Assumptions!$B$8+C25))/($A38*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>($A38*Assumptions!$B$8-(ROUND($A38*Assumptions!$B$7,0)*Assumptions!$B$8+D25))/($A38*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>($A38*Assumptions!$B$8-(ROUND($A38*Assumptions!$B$7,0)*Assumptions!$B$8+E25))/($A38*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>100</v>
+      </c>
+      <c r="B39" s="17">
+        <f>($A39*Assumptions!$B$8-(ROUND($A39*Assumptions!$B$7,0)*Assumptions!$B$8+B26))/($A39*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C39" s="17">
+        <f>($A39*Assumptions!$B$8-(ROUND($A39*Assumptions!$B$7,0)*Assumptions!$B$8+C26))/($A39*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>($A39*Assumptions!$B$8-(ROUND($A39*Assumptions!$B$7,0)*Assumptions!$B$8+D26))/($A39*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>($A39*Assumptions!$B$8-(ROUND($A39*Assumptions!$B$7,0)*Assumptions!$B$8+E26))/($A39*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>150</v>
+      </c>
+      <c r="B40" s="17">
+        <f>($A40*Assumptions!$B$8-(ROUND($A40*Assumptions!$B$7,0)*Assumptions!$B$8+B27))/($A40*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C40" s="17">
+        <f>($A40*Assumptions!$B$8-(ROUND($A40*Assumptions!$B$7,0)*Assumptions!$B$8+C27))/($A40*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>($A40*Assumptions!$B$8-(ROUND($A40*Assumptions!$B$7,0)*Assumptions!$B$8+D27))/($A40*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>($A40*Assumptions!$B$8-(ROUND($A40*Assumptions!$B$7,0)*Assumptions!$B$8+E27))/($A40*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>200</v>
+      </c>
+      <c r="B41" s="17">
+        <f>($A41*Assumptions!$B$8-(ROUND($A41*Assumptions!$B$7,0)*Assumptions!$B$8+B28))/($A41*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C41" s="17">
+        <f>($A41*Assumptions!$B$8-(ROUND($A41*Assumptions!$B$7,0)*Assumptions!$B$8+C28))/($A41*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>($A41*Assumptions!$B$8-(ROUND($A41*Assumptions!$B$7,0)*Assumptions!$B$8+D28))/($A41*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>($A41*Assumptions!$B$8-(ROUND($A41*Assumptions!$B$7,0)*Assumptions!$B$8+E28))/($A41*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>300</v>
+      </c>
+      <c r="B42" s="17">
+        <f>($A42*Assumptions!$B$8-(ROUND($A42*Assumptions!$B$7,0)*Assumptions!$B$8+B29))/($A42*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C42" s="17">
+        <f>($A42*Assumptions!$B$8-(ROUND($A42*Assumptions!$B$7,0)*Assumptions!$B$8+C29))/($A42*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D42" s="17">
+        <f>($A42*Assumptions!$B$8-(ROUND($A42*Assumptions!$B$7,0)*Assumptions!$B$8+D29))/($A42*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E42" s="17">
+        <f>($A42*Assumptions!$B$8-(ROUND($A42*Assumptions!$B$7,0)*Assumptions!$B$8+E29))/($A42*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>500</v>
+      </c>
+      <c r="B43" s="17">
+        <f>($A43*Assumptions!$B$8-(ROUND($A43*Assumptions!$B$7,0)*Assumptions!$B$8+B30))/($A43*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C43" s="17">
+        <f>($A43*Assumptions!$B$8-(ROUND($A43*Assumptions!$B$7,0)*Assumptions!$B$8+C30))/($A43*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>($A43*Assumptions!$B$8-(ROUND($A43*Assumptions!$B$7,0)*Assumptions!$B$8+D30))/($A43*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>($A43*Assumptions!$B$8-(ROUND($A43*Assumptions!$B$7,0)*Assumptions!$B$8+E30))/($A43*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>750</v>
+      </c>
+      <c r="B44" s="17">
+        <f>($A44*Assumptions!$B$8-(ROUND($A44*Assumptions!$B$7,0)*Assumptions!$B$8+B31))/($A44*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C44" s="17">
+        <f>($A44*Assumptions!$B$8-(ROUND($A44*Assumptions!$B$7,0)*Assumptions!$B$8+C31))/($A44*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D44" s="17">
+        <f>($A44*Assumptions!$B$8-(ROUND($A44*Assumptions!$B$7,0)*Assumptions!$B$8+D31))/($A44*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f>($A44*Assumptions!$B$8-(ROUND($A44*Assumptions!$B$7,0)*Assumptions!$B$8+E31))/($A44*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B45" s="17">
+        <f>($A45*Assumptions!$B$8-(ROUND($A45*Assumptions!$B$7,0)*Assumptions!$B$8+B32))/($A45*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C45" s="17">
+        <f>($A45*Assumptions!$B$8-(ROUND($A45*Assumptions!$B$7,0)*Assumptions!$B$8+C32))/($A45*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>($A45*Assumptions!$B$8-(ROUND($A45*Assumptions!$B$7,0)*Assumptions!$B$8+D32))/($A45*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>($A45*Assumptions!$B$8-(ROUND($A45*Assumptions!$B$7,0)*Assumptions!$B$8+E32))/($A45*Assumptions!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>3 · Effective cost per screen — the number that explains everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Samples / year</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>A · Today</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>B · Flat per-screen</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>C · Base + per-screen</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>D · Tiers</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>One lab test</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>25</v>
+      </c>
+      <c r="B50" s="10">
+        <f>B24/$A50</f>
+        <v/>
+      </c>
+      <c r="C50" s="10">
+        <f>C24/$A50</f>
+        <v/>
+      </c>
+      <c r="D50" s="10">
+        <f>D24/$A50</f>
+        <v/>
+      </c>
+      <c r="E50" s="10">
+        <f>E24/$A50</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="10">
+        <f>B25/$A51</f>
+        <v/>
+      </c>
+      <c r="C51" s="10">
+        <f>C25/$A51</f>
+        <v/>
+      </c>
+      <c r="D51" s="10">
+        <f>D25/$A51</f>
+        <v/>
+      </c>
+      <c r="E51" s="10">
+        <f>E25/$A51</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>100</v>
+      </c>
+      <c r="B52" s="10">
+        <f>B26/$A52</f>
+        <v/>
+      </c>
+      <c r="C52" s="10">
+        <f>C26/$A52</f>
+        <v/>
+      </c>
+      <c r="D52" s="10">
+        <f>D26/$A52</f>
+        <v/>
+      </c>
+      <c r="E52" s="10">
+        <f>E26/$A52</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>150</v>
+      </c>
+      <c r="B53" s="10">
+        <f>B27/$A53</f>
+        <v/>
+      </c>
+      <c r="C53" s="10">
+        <f>C27/$A53</f>
+        <v/>
+      </c>
+      <c r="D53" s="10">
+        <f>D27/$A53</f>
+        <v/>
+      </c>
+      <c r="E53" s="10">
+        <f>E27/$A53</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>200</v>
+      </c>
+      <c r="B54" s="10">
+        <f>B28/$A54</f>
+        <v/>
+      </c>
+      <c r="C54" s="10">
+        <f>C28/$A54</f>
+        <v/>
+      </c>
+      <c r="D54" s="10">
+        <f>D28/$A54</f>
+        <v/>
+      </c>
+      <c r="E54" s="10">
+        <f>E28/$A54</f>
+        <v/>
+      </c>
+      <c r="F54" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>300</v>
+      </c>
+      <c r="B55" s="10">
+        <f>B29/$A55</f>
+        <v/>
+      </c>
+      <c r="C55" s="10">
+        <f>C29/$A55</f>
+        <v/>
+      </c>
+      <c r="D55" s="10">
+        <f>D29/$A55</f>
+        <v/>
+      </c>
+      <c r="E55" s="10">
+        <f>E29/$A55</f>
+        <v/>
+      </c>
+      <c r="F55" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>500</v>
+      </c>
+      <c r="B56" s="10">
+        <f>B30/$A56</f>
+        <v/>
+      </c>
+      <c r="C56" s="10">
+        <f>C30/$A56</f>
+        <v/>
+      </c>
+      <c r="D56" s="10">
+        <f>D30/$A56</f>
+        <v/>
+      </c>
+      <c r="E56" s="10">
+        <f>E30/$A56</f>
+        <v/>
+      </c>
+      <c r="F56" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>750</v>
+      </c>
+      <c r="B57" s="10">
+        <f>B31/$A57</f>
+        <v/>
+      </c>
+      <c r="C57" s="10">
+        <f>C31/$A57</f>
+        <v/>
+      </c>
+      <c r="D57" s="10">
+        <f>D31/$A57</f>
+        <v/>
+      </c>
+      <c r="E57" s="10">
+        <f>E31/$A57</f>
+        <v/>
+      </c>
+      <c r="F57" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B58" s="10">
+        <f>B32/$A58</f>
+        <v/>
+      </c>
+      <c r="C58" s="10">
+        <f>C32/$A58</f>
+        <v/>
+      </c>
+      <c r="D58" s="10">
+        <f>D32/$A58</f>
+        <v/>
+      </c>
+      <c r="E58" s="10">
+        <f>E32/$A58</f>
+        <v/>
+      </c>
+      <c r="F58" s="10">
+        <f>Assumptions!$B$8</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/fluorsight-model.xlsx
+++ b/docs/fluorsight-model.xlsx
@@ -309,34 +309,6 @@
           <val>
             <numRef>
               <f>'Model'!$C$30:$C$31</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Model'!D29</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Model'!$A$30:$A$31</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Model'!$D$30:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -3319,12 +3291,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Refills</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Subscription</t>
+          <t>Fluorsight</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3306,6 @@
         <v/>
       </c>
       <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3352,12 +3318,13 @@
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="D31" s="10">
-        <f>B10</f>
-        <v/>
+        <f>B9+B10</f>
+        <v/>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Fluorsight = refills + subscription. The device is a one-off and is excluded from an annual-cost bar.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/fluorsight-model.xlsx
+++ b/docs/fluorsight-model.xlsx
@@ -506,7 +506,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>The saving holds across the rate we are least sure of</a:t>
+              <a:t>Triage pays until about 80% of screened samples escalate</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Sensitivity'!$A$6:$A$16</f>
+              <f>'Sensitivity'!$A$6:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sensitivity'!$C$6:$C$16</f>
+              <f>'Sensitivity'!$C$6:$C$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -582,7 +582,7 @@
           </tx>
           <overlay val="0"/>
         </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
@@ -3338,7 +3338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3887,6 +3887,17 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="B17" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A17,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C17" s="17">
+        <f>B17/Model!$B$6</f>
+        <v/>
+      </c>
       <c r="E17" s="10" t="n">
         <v>300</v>
       </c>
@@ -3896,6 +3907,17 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>0.6500000000000001</v>
+      </c>
+      <c r="B18" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A18,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C18" s="17">
+        <f>B18/Model!$B$6</f>
+        <v/>
+      </c>
       <c r="E18" s="10" t="n">
         <v>325</v>
       </c>
@@ -3905,6 +3927,17 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" s="20" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B19" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A19,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C19" s="17">
+        <f>B19/Model!$B$6</f>
+        <v/>
+      </c>
       <c r="E19" s="10" t="n">
         <v>350</v>
       </c>
@@ -3914,6 +3947,17 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" s="20" t="n">
+        <v>0.7500000000000001</v>
+      </c>
+      <c r="B20" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A20,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C20" s="17">
+        <f>B20/Model!$B$6</f>
+        <v/>
+      </c>
       <c r="E20" s="10" t="n">
         <v>375</v>
       </c>
@@ -3923,11 +3967,61 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B21" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A21,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C21" s="17">
+        <f>B21/Model!$B$6</f>
+        <v/>
+      </c>
       <c r="E21" s="10" t="n">
         <v>400</v>
       </c>
       <c r="F21" s="10">
         <f>Assumptions!$B$6*E21-(ROUND(Assumptions!$B$6*Assumptions!$B$7,0)*E21+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="B22" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A22,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C22" s="17">
+        <f>B22/Model!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="B23" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A23,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C23" s="17">
+        <f>B23/Model!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B24" s="10">
+        <f>Model!$B$6-(ROUND(Assumptions!$B$6*A24,0)*Assumptions!$B$8+Model!$B$9+Model!$B$10+Model!$B$11)</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>B24/Model!$B$6</f>
         <v/>
       </c>
     </row>
